--- a/Assessments/java_coding_scores_total.xlsx
+++ b/Assessments/java_coding_scores_total.xlsx
@@ -8,17 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\Empower\2025\Assessments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{271278D4-8F2A-4FD3-91EC-A1466022CC1B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B84530D8-3C48-469C-A9A9-0F26440C7D55}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{EA05622F-EDBB-4127-845F-5FE3AA375915}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{27F2ECD1-8BEA-4BCA-B8B8-FE8B947EF9CF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="java_coding_scores" localSheetId="0">Sheet1!$B$1:$G$39</definedName>
-    <definedName name="java_coding_scores_1" localSheetId="0">Sheet1!$A$1:$G$42</definedName>
-  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -28,46 +24,28 @@
 </workbook>
 </file>
 
-<file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{F4AA70D0-0FB7-48B0-90E4-0C417D436B38}" name="java_coding_scores" type="6" refreshedVersion="6" background="1" saveData="1">
-    <textPr codePage="437" sourceFile="D:\Jag\Empower\2025\Assessments\java_coding_scores.txt" comma="1">
-      <textFields count="6">
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-      </textFields>
-    </textPr>
-  </connection>
-  <connection id="2" xr16:uid="{32741541-4E46-44B4-8FAB-D26E2884AF1D}" name="java_coding_scores1" type="6" refreshedVersion="6" background="1" saveData="1">
-    <textPr codePage="437" sourceFile="D:\Jag\Empower\2025\Assessments\java_coding_scores.txt" comma="1">
-      <textFields count="7">
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-      </textFields>
-    </textPr>
-  </connection>
-</connections>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+  <si>
+    <t>ENO</t>
+  </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>Palindrome Validator</t>
-  </si>
-  <si>
-    <t>Word Occurrence Finder</t>
+    <t>Palindrome</t>
+  </si>
+  <si>
+    <t>EmployeeSalary</t>
+  </si>
+  <si>
+    <t>WordCount</t>
+  </si>
+  <si>
+    <t>PrimeGen</t>
+  </si>
+  <si>
+    <t>AgeValidator</t>
   </si>
   <si>
     <t>Srinivas M</t>
@@ -103,6 +81,9 @@
     <t>Hrithik Kumar Ukey</t>
   </si>
   <si>
+    <t>samarth kulkarni</t>
+  </si>
+  <si>
     <t>Mithun S R</t>
   </si>
   <si>
@@ -124,18 +105,18 @@
     <t>Shivlinga Halimani</t>
   </si>
   <si>
+    <t>Lalitha M</t>
+  </si>
+  <si>
     <t>Pothala Harinatha Reddy</t>
   </si>
   <si>
-    <t>Lalitha M</t>
+    <t>Divya Bhumipalli</t>
   </si>
   <si>
     <t>Keerthan K M</t>
   </si>
   <si>
-    <t>Divya Bhumipalli</t>
-  </si>
-  <si>
     <t>Syed Saud Ur Rahman</t>
   </si>
   <si>
@@ -154,58 +135,43 @@
     <t>Rupesh Prasad</t>
   </si>
   <si>
+    <t>omkar Rampure</t>
+  </si>
+  <si>
     <t>Mohit Kumar</t>
   </si>
   <si>
     <t>Rekha S</t>
   </si>
   <si>
+    <t>Hari prasad P</t>
+  </si>
+  <si>
+    <t>Sanjana S</t>
+  </si>
+  <si>
     <t>Bhuwan Chandak</t>
   </si>
   <si>
+    <t>Monisha J</t>
+  </si>
+  <si>
+    <t>Aditya Jha</t>
+  </si>
+  <si>
+    <t>Kunal Kaushik</t>
+  </si>
+  <si>
+    <t>Shri Abhishek Choudhary</t>
+  </si>
+  <si>
+    <t>YASHWANTH M</t>
+  </si>
+  <si>
     <t>Gunjan Mahajan</t>
   </si>
   <si>
-    <t>Shri Abhishek Choudhary</t>
-  </si>
-  <si>
-    <t>Kunal Kaushik</t>
-  </si>
-  <si>
-    <t>samarth kulkarni</t>
-  </si>
-  <si>
-    <t>omkar Rampure</t>
-  </si>
-  <si>
-    <t>Hari prasad P</t>
-  </si>
-  <si>
-    <t>Sanjana S</t>
-  </si>
-  <si>
-    <t>Monisha J</t>
-  </si>
-  <si>
-    <t>Aditya Jha</t>
-  </si>
-  <si>
-    <t>YASHWANTH M</t>
-  </si>
-  <si>
-    <t>ENO</t>
-  </si>
-  <si>
-    <t>Employee Salary Management</t>
-  </si>
-  <si>
-    <t>Prime Number Generator</t>
-  </si>
-  <si>
-    <t>Custom Exception - Age Validator</t>
-  </si>
-  <si>
-    <t>REEVAL</t>
+    <t>Total</t>
   </si>
 </sst>
 </file>
@@ -258,14 +224,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="java_coding_scores_1" connectionId="2" xr16:uid="{619DD142-01ED-4785-8B57-0E51217EAD7A}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
-</file>
-
-<file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="java_coding_scores" connectionId="1" xr16:uid="{A0FBDF36-C4F0-4520-AB43-8EBF119329DA}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -564,48 +522,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7632762D-2EB3-4271-BA30-97049D69C400}">
-  <dimension ref="A1:J42"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74C6E702-114C-480D-A388-6F6FF88F7BD2}">
+  <dimension ref="A1:H42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -627,12 +587,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -641,7 +601,7 @@
         <v>4</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3">
         <v>4</v>
@@ -651,42 +611,42 @@
       </c>
       <c r="H3">
         <f t="shared" ref="H3:H42" si="0">SUM(C3:G3)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -695,7 +655,7 @@
         <v>4</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -705,18 +665,18 @@
       </c>
       <c r="H5">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -725,25 +685,22 @@
         <v>3</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6">
         <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="J6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -752,115 +709,115 @@
         <v>4</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7">
         <v>4</v>
       </c>
       <c r="H7">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8">
         <v>4</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8">
         <v>4</v>
       </c>
       <c r="H8">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9">
         <v>4</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F9">
         <v>4</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H9">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C10">
         <v>4</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10">
         <v>4</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H10">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C11">
         <v>4</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11">
         <v>4</v>
@@ -870,15 +827,15 @@
       </c>
       <c r="H11">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C12">
         <v>4</v>
@@ -900,12 +857,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="C13">
         <v>4</v>
@@ -914,7 +871,7 @@
         <v>4</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13">
         <v>4</v>
@@ -924,15 +881,15 @@
       </c>
       <c r="H13">
         <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C14">
         <v>4</v>
@@ -941,7 +898,7 @@
         <v>4</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14">
         <v>4</v>
@@ -951,15 +908,15 @@
       </c>
       <c r="H14">
         <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C15">
         <v>4</v>
@@ -981,12 +938,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C16">
         <v>4</v>
@@ -1001,22 +958,22 @@
         <v>4</v>
       </c>
       <c r="G16">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H16">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17">
         <v>4</v>
@@ -1032,15 +989,15 @@
       </c>
       <c r="H17">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C18">
         <v>4</v>
@@ -1055,46 +1012,46 @@
         <v>4</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18">
         <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+      <c r="D19">
+        <v>4</v>
+      </c>
+      <c r="E19">
+        <v>3</v>
+      </c>
+      <c r="F19">
+        <v>4</v>
+      </c>
+      <c r="G19">
+        <v>4</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C19">
-        <v>4</v>
-      </c>
-      <c r="D19">
-        <v>4</v>
-      </c>
-      <c r="E19">
-        <v>4</v>
-      </c>
-      <c r="F19">
-        <v>4</v>
-      </c>
-      <c r="G19">
-        <v>4</v>
-      </c>
-      <c r="H19">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C20">
         <v>4</v>
@@ -1103,7 +1060,7 @@
         <v>4</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F20">
         <v>4</v>
@@ -1113,18 +1070,18 @@
       </c>
       <c r="H20">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D21">
         <v>4</v>
@@ -1140,15 +1097,15 @@
       </c>
       <c r="H21">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C22">
         <v>4</v>
@@ -1170,12 +1127,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C23">
         <v>4</v>
@@ -1197,12 +1154,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C24">
         <v>4</v>
@@ -1217,19 +1174,19 @@
         <v>4</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24">
         <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C25">
         <v>4</v>
@@ -1244,22 +1201,22 @@
         <v>4</v>
       </c>
       <c r="G25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H25">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26">
         <v>4</v>
@@ -1275,15 +1232,15 @@
       </c>
       <c r="H26">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C27">
         <v>4</v>
@@ -1305,12 +1262,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C28">
         <v>4</v>
@@ -1332,12 +1289,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C29">
         <v>4</v>
@@ -1359,12 +1316,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C30">
         <v>4</v>
@@ -1373,25 +1330,25 @@
         <v>4</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H30">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C31">
         <v>4</v>
@@ -1413,64 +1370,61 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C32">
         <v>4</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H32">
         <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="J32" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C33">
         <v>3</v>
       </c>
       <c r="D33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F33">
         <v>4</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H33">
         <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1481,7 +1435,7 @@
         <v>4</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34">
         <v>4</v>
@@ -1494,10 +1448,10 @@
       </c>
       <c r="H34">
         <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1505,31 +1459,31 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35">
         <v>3</v>
       </c>
       <c r="F35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H35">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C36">
         <v>4</v>
@@ -1538,7 +1492,7 @@
         <v>3</v>
       </c>
       <c r="E36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F36">
         <v>4</v>
@@ -1548,48 +1502,48 @@
       </c>
       <c r="H36">
         <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C37">
         <v>4</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F37">
         <v>4</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H37">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38">
         <v>3</v>
@@ -1602,21 +1556,21 @@
       </c>
       <c r="H38">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C39">
         <v>4</v>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E39">
         <v>4</v>
@@ -1625,25 +1579,22 @@
         <v>4</v>
       </c>
       <c r="G39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H39">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="J39" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D40">
         <v>2</v>
@@ -1652,22 +1603,22 @@
         <v>2</v>
       </c>
       <c r="F40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H40">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C41">
         <v>4</v>
@@ -1676,7 +1627,7 @@
         <v>4</v>
       </c>
       <c r="E41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F41">
         <v>4</v>
@@ -1686,34 +1637,34 @@
       </c>
       <c r="H41">
         <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D42">
         <v>4</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F42">
         <v>4</v>
       </c>
       <c r="G42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H42">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
